--- a/05_Figures/F06_prediction/proteins/T3/comp_hypertrophy/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T3/comp_hypertrophy/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -143,21 +143,24 @@
     <t xml:space="preserve">PPIF</t>
   </si>
   <si>
+    <t xml:space="preserve">AKR1C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2S3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSF2</t>
+  </si>
+  <si>
     <t xml:space="preserve">AK1</t>
   </si>
   <si>
-    <t xml:space="preserve">AKR1C3</t>
+    <t xml:space="preserve">BDH1</t>
   </si>
   <si>
     <t xml:space="preserve">BSG</t>
   </si>
   <si>
-    <t xml:space="preserve">EIF2S3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACSF2</t>
-  </si>
-  <si>
     <t xml:space="preserve">EIF4A2</t>
   </si>
   <si>
@@ -179,150 +182,162 @@
     <t xml:space="preserve">RAD23B</t>
   </si>
   <si>
+    <t xml:space="preserve">RPL12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1H1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESYT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGAM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN3</t>
+  </si>
+  <si>
     <t xml:space="preserve">SDHA</t>
   </si>
   <si>
-    <t xml:space="preserve">ACAT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT1</t>
+    <t xml:space="preserve">FITM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDHD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPLOC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM20D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TNPO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LNPK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPM1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMEM11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHCHD7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSDL2</t>
   </si>
   <si>
     <t xml:space="preserve">MYO18A</t>
   </si>
   <si>
-    <t xml:space="preserve">PGAM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTN3</t>
+    <t xml:space="preserve">PPP3CB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPTIN9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCHL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH3A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYB5R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAXE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP1R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNTA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUCLG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOLLIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADVL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFG3L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIFM1</t>
   </si>
   <si>
     <t xml:space="preserve">ALPK3</t>
   </si>
   <si>
-    <t xml:space="preserve">CAMK2D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1H1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LDHD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPLOC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPM1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEPTIN9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VARS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHCHD7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSDL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LNPK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PM20D2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP3CB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCHL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH3A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAXE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1R2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNTA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUCLG1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACAA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACADVL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACSL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTR1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFG3L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIFM1</t>
-  </si>
-  <si>
     <t xml:space="preserve">ATP5MF</t>
   </si>
   <si>
@@ -332,16 +347,16 @@
     <t xml:space="preserve">CA3</t>
   </si>
   <si>
-    <t xml:space="preserve">CANX</t>
-  </si>
-  <si>
     <t xml:space="preserve">CAPZA2</t>
   </si>
   <si>
     <t xml:space="preserve">CLIP1</t>
   </si>
   <si>
-    <t xml:space="preserve">CYB5R1</t>
+    <t xml:space="preserve">COPZ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS</t>
   </si>
   <si>
     <t xml:space="preserve">DHRS7</t>
@@ -353,7 +368,7 @@
     <t xml:space="preserve">DLST</t>
   </si>
   <si>
-    <t xml:space="preserve">DYSF</t>
+    <t xml:space="preserve">DYNC1LI1</t>
   </si>
   <si>
     <t xml:space="preserve">ECI2</t>
@@ -362,7 +377,7 @@
     <t xml:space="preserve">EIF3E</t>
   </si>
   <si>
-    <t xml:space="preserve">EIF5B</t>
+    <t xml:space="preserve">ERP44</t>
   </si>
   <si>
     <t xml:space="preserve">FAM98B</t>
@@ -386,9 +401,24 @@
     <t xml:space="preserve">MAP2K2</t>
   </si>
   <si>
+    <t xml:space="preserve">MAP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPK9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPRE3</t>
+  </si>
+  <si>
     <t xml:space="preserve">MCCC2</t>
   </si>
   <si>
+    <t xml:space="preserve">MRPL12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS18B</t>
+  </si>
+  <si>
     <t xml:space="preserve">MTARC2</t>
   </si>
   <si>
@@ -398,12 +428,18 @@
     <t xml:space="preserve">MYBPH</t>
   </si>
   <si>
+    <t xml:space="preserve">MYH14</t>
+  </si>
+  <si>
     <t xml:space="preserve">NAPRT</t>
   </si>
   <si>
     <t xml:space="preserve">NEK7</t>
   </si>
   <si>
+    <t xml:space="preserve">NIPSNAP2</t>
+  </si>
+  <si>
     <t xml:space="preserve">NNMT</t>
   </si>
   <si>
@@ -434,12 +470,18 @@
     <t xml:space="preserve">PRKACA</t>
   </si>
   <si>
+    <t xml:space="preserve">PSMD2</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSMD7</t>
   </si>
   <si>
     <t xml:space="preserve">PSMD8</t>
   </si>
   <si>
+    <t xml:space="preserve">PTPN11</t>
+  </si>
+  <si>
     <t xml:space="preserve">RCN1</t>
   </si>
   <si>
@@ -455,13 +497,13 @@
     <t xml:space="preserve">RPL13A</t>
   </si>
   <si>
+    <t xml:space="preserve">RPL7A</t>
+  </si>
+  <si>
     <t xml:space="preserve">RPLP1</t>
   </si>
   <si>
-    <t xml:space="preserve">RWDD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A1</t>
+    <t xml:space="preserve">RTCB</t>
   </si>
   <si>
     <t xml:space="preserve">SCFD1</t>
@@ -482,10 +524,10 @@
     <t xml:space="preserve">TCAP</t>
   </si>
   <si>
-    <t xml:space="preserve">TNPO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOLLIP</t>
+    <t xml:space="preserve">THOP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMEM167A</t>
   </si>
   <si>
     <t xml:space="preserve">TPP2</t>
@@ -884,16 +926,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.103771909652197</v>
+        <v>-0.133066409911006</v>
       </c>
       <c r="I2" t="n">
-        <v>0.182142857142857</v>
+        <v>0.0678571428571429</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -917,29 +959,21 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.103771909652197</v>
+        <v>-0.133066409911006</v>
       </c>
       <c r="I3" t="n">
-        <v>0.182142857142857</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.18407960199005</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.208955223880597</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.770400551951752</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.741878884946743</v>
-      </c>
+        <v>0.0678571428571429</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -963,2206 +997,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1.93157745712131</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-1.21792930523669</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.410679992528748</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.820631047876561</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.390153775442054</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.589476956059504</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-1.87906684319438</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.301657020857741</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.0659297815713085</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.78405515195383</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.456936062153335</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.278622720124873</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.917176416243048</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-2.00012022330162</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.523293784908059</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-1.4440081944987</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.372159678790082</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.487435660046484</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.00588306185046583</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-1.98746534092201</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.411142797816387</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.721360398825408</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-3.25114928487947</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.480728418323118</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.0133553573003554</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.441403253253561</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.358701173050585</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.376214904534415</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.553696689736784</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.653589953684879</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-1.06194957296575</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.541090415083716</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.0575643194779247</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-1.27517834608123</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.198240102779348</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.531743783027046</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.251736301313879</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-1.29528846700118</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.488809269812811</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-1.62110753297771</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.954717591357144</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.738692451829437</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-1.10059953336279</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.237464643193732</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.666606041343113</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.0590545395238417</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-3.78770698642521</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.44808231463966</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-1.03240912041174</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.977653001326724</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-1.15764730058278</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.175667580840982</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.162797227496804</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.405537077534099</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.181771863753814</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-2.37801668130741</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.70634145731347</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.515766819378064</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-1.37010773835962</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.0328963086020133</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.138447341946786</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.627941243071788</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-2.31475480964264</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.723514154417533</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-1.4297842147517</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-1.01901410367543</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-1.23401296450061</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-1.52603600174787</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0.0226415609502598</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0.202282889925228</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-2.38288146802277</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.467484621674984</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.109159851996203</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.321671023314292</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.046686576364557</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.235616861273888</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.847460244391091</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-1.69342230962335</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.816205097992879</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.624158136057397</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.449358277687051</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-1.37137971858281</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.887352248547401</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.577687886503896</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.0835375849381796</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.611917430788067</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.419413382802683</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.892766442767349</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.0809009659730404</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-0.759917242194798</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.945893634585576</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.157881914200782</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.80488392789259</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-1.86669555380807</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0.0512074344955206</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-1.65764231795588</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.371843652167257</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0.00965860107069949</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-2.75040760067216</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-1.57988750422639</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-3.0189141591688</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.101064671863071</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.386064399486981</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.826076699228753</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>0.00307242561420762</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.313157808165392</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.949465247637007</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-1.23015096071941</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.365563941491893</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.541313201701774</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-1.06403050633256</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.759947487998474</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.61740400568963</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.63103273949396</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-1.36885681552073</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-1.16033911677408</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.223810594547004</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-1.19763130574664</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-0.675024905570796</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-1.03310127557363</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.885217504220818</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-0.63749008052653</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-1.56560698675206</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.833362892612688</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-1.10274603572666</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.294712226222419</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.759749165896701</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-1.34103080686846</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-3.5968652099492</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.275771447317087</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-1.45137950382881</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.0848325786827613</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-1.46539365353806</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-1.37193635425453</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.694916136572457</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-1.09924945361498</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.913476068088304</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.896547734244728</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.311912081666883</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>0.00179472547082205</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-1.09737730525325</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>0.20207956339159</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>0.601422621094902</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.844589992938907</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-0.282415896222444</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-1.2043359258743</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.725505557099622</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.746876336580446</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.541757471023107</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.253550684056205</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.652884359937072</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.780335218416184</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.331417787345644</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-1.26072888767847</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-1.18053294763089</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.798123835469115</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.394955202079882</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.896759413843169</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>0.0768308492123705</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.435767544503832</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.641105436189062</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.236982548835616</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.526008270147711</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.855653653759931</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.421291435154763</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-1.72246417274549</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-2.18200046502997</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.185824195996948</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.410758093260564</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-1.72947560594485</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-0.547278054776281</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.807224883432324</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-0.0162867878626296</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.266389884541687</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.745067391413416</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.667022549425539</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-1.36233272786568</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-1.58507251563039</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>0.364303495307394</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.667223778804563</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.915711830874146</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.0918491361442164</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.672449882279968</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-1.41360971182105</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>0.104656913489919</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.634558168616984</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.778156133532854</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.789985512679384</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.806829176833029</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-0.232983547277815</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.957009278812723</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.56483970410296</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-2.10447242195923</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-1.07839724486984</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-1.08308143197551</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.410422667643254</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-1.01402001579837</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-1.96184056781046</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-1.14514194406675</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.204039814714461</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3205,7 +1039,7 @@
         <v>9.43</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3670883133082</v>
+        <v>6.51159847014204</v>
       </c>
     </row>
     <row r="3">
@@ -3222,7 +1056,7 @@
         <v>20.73</v>
       </c>
       <c r="E3" t="n">
-        <v>3.43449045546922</v>
+        <v>3.4913340030949</v>
       </c>
     </row>
     <row r="4">
@@ -3239,7 +1073,7 @@
         <v>13.69</v>
       </c>
       <c r="E4" t="n">
-        <v>2.04320711234189</v>
+        <v>2.1211553255125</v>
       </c>
     </row>
     <row r="5">
@@ -3256,7 +1090,7 @@
         <v>10.45</v>
       </c>
       <c r="E5" t="n">
-        <v>0.949417773244213</v>
+        <v>0.840882024501892</v>
       </c>
     </row>
     <row r="6">
@@ -3273,7 +1107,7 @@
         <v>14.93</v>
       </c>
       <c r="E6" t="n">
-        <v>23.5236910115466</v>
+        <v>18.3828764872162</v>
       </c>
     </row>
     <row r="7">
@@ -3290,7 +1124,7 @@
         <v>13.79</v>
       </c>
       <c r="E7" t="n">
-        <v>2.88017613802725</v>
+        <v>1.92368470415317</v>
       </c>
     </row>
     <row r="8">
@@ -3307,7 +1141,7 @@
         <v>8.06</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.70330002544216</v>
+        <v>-2.11638760865536</v>
       </c>
     </row>
     <row r="9">
@@ -3324,7 +1158,7 @@
         <v>0.79</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4115865642102</v>
+        <v>2.29243619529669</v>
       </c>
     </row>
     <row r="10">
@@ -3341,7 +1175,7 @@
         <v>0.85</v>
       </c>
       <c r="E10" t="n">
-        <v>1.42927239766294</v>
+        <v>7.59653340156003</v>
       </c>
     </row>
     <row r="11">
@@ -3358,7 +1192,7 @@
         <v>-4.09</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.05622196022971</v>
+        <v>-6.98056719513449</v>
       </c>
     </row>
     <row r="12">
@@ -3375,7 +1209,7 @@
         <v>-0.74</v>
       </c>
       <c r="E12" t="n">
-        <v>1.83479562700268</v>
+        <v>1.68980420330309</v>
       </c>
     </row>
     <row r="13">
@@ -3392,7 +1226,7 @@
         <v>-1.86</v>
       </c>
       <c r="E13" t="n">
-        <v>9.19254260594466</v>
+        <v>9.14341804603166</v>
       </c>
     </row>
     <row r="14">
@@ -3409,7 +1243,7 @@
         <v>-6.6</v>
       </c>
       <c r="E14" t="n">
-        <v>2.22942488247976</v>
+        <v>3.04620277272974</v>
       </c>
     </row>
     <row r="15">
@@ -3426,7 +1260,7 @@
         <v>-5.99</v>
       </c>
       <c r="E15" t="n">
-        <v>4.012781266467</v>
+        <v>4.21660916326656</v>
       </c>
     </row>
     <row r="16">
@@ -3443,7 +1277,7 @@
         <v>-0.48</v>
       </c>
       <c r="E16" t="n">
-        <v>2.15379600568056</v>
+        <v>2.70012509488244</v>
       </c>
     </row>
   </sheetData>
@@ -3502,10 +1336,10 @@
         <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>0.933333333333333</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -3519,10 +1353,10 @@
         <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
@@ -3536,10 +1370,10 @@
         <v>41</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.533333333333333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6">
@@ -3553,10 +1387,10 @@
         <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3570,10 +1404,10 @@
         <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -3621,10 +1455,10 @@
         <v>46</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -3638,10 +1472,10 @@
         <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="12">
@@ -3655,10 +1489,10 @@
         <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -3672,10 +1506,10 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -3689,10 +1523,10 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -3706,10 +1540,10 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="16">
@@ -3723,10 +1557,10 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="17">
@@ -3740,10 +1574,10 @@
         <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -3757,10 +1591,10 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="19">
@@ -3774,10 +1608,10 @@
         <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.333333333333333</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="20">
@@ -3791,10 +1625,10 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21">
@@ -3808,10 +1642,10 @@
         <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22">
@@ -3825,10 +1659,10 @@
         <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23">
@@ -3842,10 +1676,10 @@
         <v>59</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24">
@@ -3859,10 +1693,10 @@
         <v>60</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="25">
@@ -3876,10 +1710,10 @@
         <v>61</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="26">
@@ -3893,10 +1727,10 @@
         <v>62</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="27">
@@ -3910,10 +1744,10 @@
         <v>63</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>0.266666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28">
@@ -3927,10 +1761,10 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -3944,10 +1778,10 @@
         <v>65</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -3961,10 +1795,10 @@
         <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="31">
@@ -3978,10 +1812,10 @@
         <v>67</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="32">
@@ -3995,10 +1829,10 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="33">
@@ -4012,10 +1846,10 @@
         <v>69</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="34">
@@ -4114,10 +1948,10 @@
         <v>75</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="40">
@@ -4267,10 +2101,10 @@
         <v>84</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="49">
@@ -4471,10 +2305,10 @@
         <v>96</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="61">
@@ -4488,10 +2322,10 @@
         <v>97</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="62">
@@ -4505,10 +2339,10 @@
         <v>98</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="63">
@@ -4522,10 +2356,10 @@
         <v>99</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="64">
@@ -5562,6 +3396,244 @@
         <v>1</v>
       </c>
       <c r="E124" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="s">
+        <v>161</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="s">
+        <v>162</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="s">
+        <v>163</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="s">
+        <v>164</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="s">
+        <v>165</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="s">
+        <v>166</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="s">
+        <v>167</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="s">
+        <v>168</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="s">
+        <v>169</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="s">
+        <v>170</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="s">
+        <v>171</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="s">
+        <v>172</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="s">
+        <v>173</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="s">
+        <v>174</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/T3/comp_hypertrophy/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T3/comp_hypertrophy/spls/c_data/results.xlsx
@@ -962,7 +962,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.133066409911006</v>
@@ -970,10 +970,18 @@
       <c r="I3" t="n">
         <v>0.0678571428571429</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.18407960199005</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.278606965174129</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.765519304337054</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.71437290562802</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -997,6 +1005,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-2.11541613415468</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.3378894622719</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.268466617934367</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.672677868152477</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.25888127757744</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.718050215475974</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-2.26454226523666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.348285414829348</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.146393392115887</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.76801257723167</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.53977474001575</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.229753634462477</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.817783688639333</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-2.14197144294548</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.500894096969158</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.2815718880987</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.308039067877996</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.889475703376943</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.0550702381794638</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-2.11693490219725</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0308345570128021</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.782116401935541</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-2.54377032396184</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.67310631602807</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.107965213501141</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.291189755646682</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.448075579534819</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.272491369745902</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.362807418501935</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.899003591209256</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-1.14775558019891</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.484611911646545</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.0363126697297307</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-1.27456188575706</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.344657753817234</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.411240287166913</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.361669986186795</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-1.59693296132307</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.544095733524438</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-1.6920978695544</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-1.01069295165605</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.820533531553312</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-1.08025994266565</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.190614125756213</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.04251728494068</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0760709583973027</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-3.1806994985266</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.456192891243541</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.908070659663114</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-1.62658073574543</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.830127473673819</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.0569566036569977</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.161990804233325</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.345172377974966</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.370985428624355</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-2.44834318091631</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.56562562109836</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.484394977297557</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-1.60743611504459</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.026949434358656</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.157694107982449</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.698128700487626</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-1.09354777032577</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.762347767603086</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-1.37933850441098</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-1.00051840365755</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-1.2156902724367</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-1.47419598444867</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.0258064842726005</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.251003442219758</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.986417495053121</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.762296387092567</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.187451946097427</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.355407161228257</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.0214959580497077</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.0165190897326868</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.801480291916038</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-1.76554398945033</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.571007262685751</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.566815073572086</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.292491895342266</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-1.35565304094887</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.796397930214005</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.630473755211973</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.0792659890256807</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.538409636627313</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.475205350026331</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.872088151923416</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.0790717508997365</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.646230280788002</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.713145990301946</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.213351851326269</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-1.55212494163376</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-1.84242033854204</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.0340768449195854</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-2.19423467391463</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.40596051832497</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.0940753776603687</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-2.72663174555596</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-1.79790429245704</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.17945596039889</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.0728061178545603</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.396255145221675</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.652084814230302</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.0902546317680166</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.230914131542084</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-1.06900896342879</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-1.00886390063882</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.435251560280768</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.403668990222994</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-1.02339531634205</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.731683072509743</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.517201878935393</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.665469163987834</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-1.41614469775886</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-1.33829569720389</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.149909557406511</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-2.78480773006977</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.574108196277833</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.94672587139132</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.868357093634932</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.768004062007367</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-1.45301852997194</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.789467620480478</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-1.07652701755699</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.276617047865494</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.745632460386339</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-1.17690239889026</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-3.33381844250028</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.296235404171895</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-1.4387001106197</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.461795145692416</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-1.59438072134293</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-1.27933920389499</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.665598384787915</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.0728592437976381</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.766924581004721</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.949613440572123</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.507328369046806</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.0822921796718055</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.955731774648257</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.191886507743961</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.60631726098993</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.887810180941667</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.176295253869793</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-1.64137501046506</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-1.02903540472847</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.669461088422983</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.560041162538888</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.273042026183703</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.670933073486472</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.811551011630546</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.158749279472417</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-1.24958871151865</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-1.67820863681388</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.787390464252422</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.501122876951696</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.791846326011552</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0.578378722816878</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.127278230247637</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.710476448600194</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.0712365816241713</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.781954716082106</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.747578804866805</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.54632221259254</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1.50799969200303</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-1.75978058879662</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.0517572867584579</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.556023825268538</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-1.912150962605</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.508821992748389</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-1.98082334319451</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-0.315358276814047</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.322043084535238</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.815895253011915</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.52535563544186</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-1.35340679803319</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1.57757310622197</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.189514900464972</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.646433322073614</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.829061360773479</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.165710622399292</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.538763951247616</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-1.39066688051165</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.126058154567247</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.611622743603121</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.785109507713738</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.815541455852161</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.782983232650547</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.480131603212788</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-1.11311012367859</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.547465341174266</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-1.74591332749562</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.973988556017471</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.953668038390384</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.424313687481463</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.978143176768824</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-1.88724257848778</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-1.15581449083157</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.177424414561526</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
